--- a/public/templates/OArm_Template.xlsx
+++ b/public/templates/OArm_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:M53"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1231,16 +1231,16 @@
         <v>Time (sec)</v>
       </c>
       <c r="E42" t="str">
-        <v>Workload</v>
+        <v>Workload (mA·min/week)</v>
       </c>
       <c r="F42" t="str">
+        <v>Tol Value</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Tol Operator</v>
+      </c>
+      <c r="H42" t="str">
         <v>Location</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Left</v>
-      </c>
-      <c r="H42" t="str">
-        <v>Right</v>
       </c>
       <c r="I42" t="str">
         <v>Front</v>
@@ -1249,6 +1249,12 @@
         <v>Back</v>
       </c>
       <c r="K42" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Right</v>
+      </c>
+      <c r="M42" t="str">
         <v>Top</v>
       </c>
     </row>
@@ -1269,21 +1275,27 @@
         <v>500</v>
       </c>
       <c r="F43" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G43" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="H43" t="str">
         <v>Tube</v>
       </c>
-      <c r="G43" t="str">
+      <c r="I43" t="str">
         <v>0.05</v>
       </c>
-      <c r="H43" t="str">
+      <c r="J43" t="str">
         <v>0.03</v>
       </c>
-      <c r="I43" t="str">
+      <c r="K43" t="str">
         <v>0.06</v>
       </c>
-      <c r="J43" t="str">
+      <c r="L43" t="str">
         <v>0.04</v>
       </c>
-      <c r="K43" t="str">
+      <c r="M43" t="str">
         <v>0.02</v>
       </c>
     </row>
@@ -1304,22 +1316,28 @@
         <v/>
       </c>
       <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
         <v>Collimator</v>
       </c>
-      <c r="G44" t="str">
+      <c r="I44" t="str">
         <v>0.02</v>
       </c>
-      <c r="H44" t="str">
+      <c r="J44" t="str">
         <v>0.02</v>
       </c>
-      <c r="I44" t="str">
+      <c r="K44" t="str">
         <v>0.03</v>
       </c>
-      <c r="J44" t="str">
+      <c r="L44" t="str">
         <v>0.01</v>
       </c>
-      <c r="K44" t="str">
-        <v>0.01</v>
+      <c r="M44" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1580,14 +1598,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M53"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:M48"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -2347,16 +2365,16 @@
         <v>Time (sec)</v>
       </c>
       <c r="E36" t="str">
-        <v>Workload</v>
+        <v>Workload (mA·min/week)</v>
       </c>
       <c r="F36" t="str">
+        <v>Tol Value</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Tol Operator</v>
+      </c>
+      <c r="H36" t="str">
         <v>Location</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Left</v>
-      </c>
-      <c r="H36" t="str">
-        <v>Right</v>
       </c>
       <c r="I36" t="str">
         <v>Front</v>
@@ -2365,6 +2383,12 @@
         <v>Back</v>
       </c>
       <c r="K36" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Right</v>
+      </c>
+      <c r="M36" t="str">
         <v>Top</v>
       </c>
     </row>
@@ -2385,21 +2409,27 @@
         <v>500</v>
       </c>
       <c r="F37" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G37" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="H37" t="str">
         <v>Tube</v>
       </c>
-      <c r="G37" t="str">
+      <c r="I37" t="str">
         <v>0.05</v>
       </c>
-      <c r="H37" t="str">
+      <c r="J37" t="str">
         <v>0.03</v>
       </c>
-      <c r="I37" t="str">
+      <c r="K37" t="str">
         <v>0.06</v>
       </c>
-      <c r="J37" t="str">
+      <c r="L37" t="str">
         <v>0.04</v>
       </c>
-      <c r="K37" t="str">
+      <c r="M37" t="str">
         <v>0.02</v>
       </c>
     </row>
@@ -2420,22 +2450,28 @@
         <v/>
       </c>
       <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
         <v>Collimator</v>
       </c>
-      <c r="G38" t="str">
+      <c r="I38" t="str">
         <v>0.02</v>
       </c>
-      <c r="H38" t="str">
+      <c r="J38" t="str">
         <v>0.02</v>
       </c>
-      <c r="I38" t="str">
+      <c r="K38" t="str">
         <v>0.03</v>
       </c>
-      <c r="J38" t="str">
+      <c r="L38" t="str">
         <v>0.01</v>
       </c>
-      <c r="K38" t="str">
-        <v>0.01</v>
+      <c r="M38" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2728,7 +2764,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/OArm_Template.xlsx
+++ b/public/templates/OArm_Template.xlsx
@@ -653,7 +653,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>mA Station 1</v>
+        <v>mAs Station 1</v>
       </c>
       <c r="B12" t="str">
         <v>50</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mA Station 2</v>
+        <v>mAs Station 2</v>
       </c>
       <c r="B13" t="str">
         <v>100</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mA Station 3</v>
+        <v>mAs Station 3</v>
       </c>
       <c r="B14" t="str">
         <v>200</v>
@@ -1011,19 +1011,19 @@
         <v>mAs</v>
       </c>
       <c r="C24" t="str">
-        <v>Meas 1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="D24" t="str">
-        <v>Meas 2</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="E24" t="str">
-        <v>Meas 3</v>
+        <v>Measured Output 3</v>
       </c>
       <c r="F24" t="str">
-        <v>Meas 4</v>
+        <v>Measured Output 4</v>
       </c>
       <c r="G24" t="str">
-        <v>Meas 5</v>
+        <v>Measured Output 5</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>mA Station 1</v>
+        <v>mAs Station 1</v>
       </c>
       <c r="B6" t="str">
         <v>50</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mA Station 2</v>
+        <v>mAs Station 2</v>
       </c>
       <c r="B7" t="str">
         <v>100</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>mA Station 3</v>
+        <v>mAs Station 3</v>
       </c>
       <c r="B8" t="str">
         <v>200</v>
@@ -2145,19 +2145,19 @@
         <v>mAs</v>
       </c>
       <c r="C18" t="str">
-        <v>Meas 1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="D18" t="str">
-        <v>Meas 2</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="E18" t="str">
-        <v>Meas 3</v>
+        <v>Measured Output 3</v>
       </c>
       <c r="F18" t="str">
-        <v>Meas 4</v>
+        <v>Measured Output 4</v>
       </c>
       <c r="G18" t="str">
-        <v>Meas 5</v>
+        <v>Measured Output 5</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>mAs Range</v>
+        <v>mAs</v>
       </c>
       <c r="B42" t="str">
         <v>Measured Output 1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>5 - 10</v>
+        <v>5</v>
       </c>
       <c r="B43" t="str">
         <v>0.50</v>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>10 - 20</v>
+        <v>10</v>
       </c>
       <c r="B44" t="str">
         <v>1.00</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>20 - 50</v>
+        <v>20</v>
       </c>
       <c r="B45" t="str">
         <v>2.50</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>50 - 100</v>
+        <v>50</v>
       </c>
       <c r="B46" t="str">
         <v>5.00</v>
